--- a/test-data/Sample_Test_Data.xlsx
+++ b/test-data/Sample_Test_Data.xlsx
@@ -466,6 +466,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -580,7 +581,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Fixed denomination Blackhawk</t>
+          <t>Fixed denomination Gift Card Provider</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -636,12 +637,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Return DL barcode</t>
+          <t>Return customer ID barcode</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>TLOG stores state + DL + source=barcode</t>
+          <t>Audit log stores state + customer ID + source=barcode</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
@@ -664,12 +665,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Manual DL fallback</t>
+          <t>Manual customer ID fallback</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>TLOG stores source=manual</t>
+          <t>Audit log stores source=manual</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
